--- a/Employee_Reports_wi48/Rolly Miano Valdez Q0611.xlsx
+++ b/Employee_Reports_wi48/Rolly Miano Valdez Q0611.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1538,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1651,53 +1651,53 @@
       <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-009</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-041</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>28-Jul-2025</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>28-Jul-2026</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>10-Apr-2027</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
+          <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-010</t>
+          <t>LSME-CRG-SOP-009</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1734,11 +1734,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1754,85 +1754,85 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-010</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>28-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>28-Jul-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>06-Aug-2025</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>06-Aug-2026</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="H29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-011</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>31-Aug-2025</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>31-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+          <t>Replacing Bearings Of ULD Hoist Counterweight Pulley (SOPs)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-018</t>
+          <t>LSME-CRG-SOP-011</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1869,11 +1869,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1889,28 +1889,40 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
+          <t>Overload and Load Testing Procedure In ULD Hoist (SOPs)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-018</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
+          <t>31-Aug-2025</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2026</t>
+          <t>31-Aug-2026</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1926,48 +1938,85 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
+          <t>ULD Hoist Drve Motor Replacement (SOPs)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>24-Nov-2025</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>24-Nov-2026</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>Equipment Teaching Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-027</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>09-Jan-2026</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>09-Jan-2027</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2386,7 +2435,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2415,7 +2464,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2444,7 +2493,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2473,7 +2522,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7964</v>
+        <v>7961</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2502,7 +2551,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2525,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2583,21 +2632,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ews 20ft</t>
+          <t>stacker crane</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2612,21 +2661,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ews 10 ft</t>
+          <t>h9tv</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>25-May-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>19-Apr-2048</t>
+          <t>03-Jun-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7951</v>
+        <v>7993</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2641,21 +2690,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>ews 20ft</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7957</v>
+        <v>7948</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2670,21 +2719,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>truckdock 15ft</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>30-May-2026</t>
+          <t>25-May-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>24-Apr-2048</t>
+          <t>19-Apr-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2699,21 +2748,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>truckdock  20ft</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7955</v>
+        <v>7954</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2728,7 +2777,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>turntable</t>
+          <t>truckdock 15ft</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2742,7 +2791,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2757,21 +2806,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>truckdock  20ft</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>31-May-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>25-Apr-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7957</v>
+        <v>7952</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2786,21 +2835,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>uldtv 20ft</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>30-May-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>24-Apr-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7958</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2815,21 +2864,21 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>uldtv 15ft</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>31-May-2026</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>26-Apr-2048</t>
+          <t>25-Apr-2048</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7958</v>
+        <v>7954</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2844,21 +2893,21 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>bbtv 20ft</t>
+          <t>uldtv 20ft</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2873,21 +2922,21 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>bbtv 15ft</t>
+          <t>uldtv 15ft</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>12-Jun-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>07-May-2048</t>
+          <t>26-Apr-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7955</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2902,21 +2951,21 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>bbtv 20ft</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7950</v>
+        <v>7966</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2931,21 +2980,21 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>bbtv 15ft</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>26-May-2026</t>
+          <t>12-Jun-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2048</t>
+          <t>07-May-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7952</v>
+        <v>7966</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2960,21 +3009,21 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>fmc deck</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>29-May-2026</t>
+          <t>24-May-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2048</t>
+          <t>18-Apr-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2989,21 +3038,21 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>cs placing deck</t>
+          <t>powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>26-May-2026</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>16-May-2048</t>
+          <t>20-Apr-2048</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7978</v>
+        <v>7949</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3018,21 +3067,21 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>cs input and output conveyor</t>
+          <t>non powered roller deckmatarsop</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>21-Jun-2026</t>
+          <t>29-May-2026</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16-May-2048</t>
+          <t>23-Apr-2048</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7978</v>
+        <v>7952</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3047,21 +3096,21 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ball deck</t>
+          <t>cs placing deck</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>24-May-2026</t>
+          <t>21-Jun-2026</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>18-Apr-2048</t>
+          <t>16-May-2048</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7950</v>
+        <v>7975</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3076,28 +3125,86 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>cs input and output conveyor</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>21-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>16-May-2048</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7975</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>24-May-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>18-Apr-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7947</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>floor scale</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>26-May-2026</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>20-Apr-2048</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>7952</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
+        <v>7949</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
